--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4074074074074074</v>
+        <v>0.556390977443609</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4084507042253521</v>
+        <v>0.5563380281690141</v>
       </c>
       <c r="D2">
-        <v>0.6043165467625899</v>
+        <v>0.4598540145985401</v>
       </c>
       <c r="E2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.556390977443609</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5563380281690141</v>
+        <v>0.5774647887323944</v>
       </c>
       <c r="D2">
-        <v>0.4598540145985401</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="E2">
         <v>133</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
